--- a/program/산출물양식/[기획] 에이전트 기능 정의서_여행.xlsx
+++ b/program/산출물양식/[기획] 에이전트 기능 정의서_여행.xlsx
@@ -566,6 +566,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -664,6 +665,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
@@ -717,6 +719,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -1130,6 +1133,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
@@ -1196,6 +1200,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -1504,6 +1509,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
@@ -1565,6 +1571,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -2442,6 +2449,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
@@ -2465,7 +2473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2705,22 +2713,22 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>list_cases</t>
+          <t>tripilot_list_trips</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>app/presentation/api/mcp.py</t>
+          <t>GET /v1/web/trips</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>[실측] 구현</t>
+          <t>[실측] 구현 · 읽기</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>required_scope = mcp:read</t>
+          <t>내 여행 목록</t>
         </is>
       </c>
     </row>
@@ -2732,22 +2740,22 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>get_case_detail</t>
+          <t>tripilot_get_trip</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>app/presentation/api/mcp.py</t>
+          <t>GET /v1/web/trips/{id}</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>[실측] 구현</t>
+          <t>[실측] 구현 · 읽기</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>required_scope = mcp:read</t>
+          <t>일정 — 항목마다 식사·활동·이동 구분 · 끼니 · 시각 · 장소 정보 · 다른 안. 그날만 보기 가능</t>
         </is>
       </c>
     </row>
@@ -2759,22 +2767,22 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>open_support_case</t>
+          <t>tripilot_get_notices</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>app/presentation/api/mcp.py</t>
+          <t>GET /v1/web/trips/{id}/notices</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>[실측] 구현</t>
+          <t>[실측] 구현 · 읽기</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>required_scope = mcp:read. Case 를 만들지만 바깥 세계를 안 바꾸므로 read 로 본다</t>
+          <t>서버가 보낸 알림 전부</t>
         </is>
       </c>
     </row>
@@ -2786,41 +2794,404 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
+          <t>tripilot_get_proposals</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>GET /v1/web/trips/{id}/proposals</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>[실측] 구현 · 읽기</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>「바꿀까요?」 하고 물어 둔 대기 제안</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>MCP</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>tripilot_get_itinerary_schema</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>app/modules/travel_ops/trip_api.py CreateTrip</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>[실측] 구현 · 읽기</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>일정 등록 JSON 스키마(customer_id 는 뺀다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>MCP</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>tripilot_ask</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>POST /v1/web/trips/{id}/messages</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>[실측] 구현 · 쓰기(스위치)</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>자유 문장을 여행 창구에 전한다 — 질문은 사실로 답하고 요청은 조건 확인 뒤 변경</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>MCP</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>tripilot_report_issue</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>POST /v1/web/trips/{id}/reports</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>[실측] 구현 · 쓰기(스위치)</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>지연 · 휴무 · 품절 신고 — 서버가 판정해 일정을 바꾸거나 선택지를 돌려준다</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>MCP</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>tripilot_swap_item</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>POST /v1/web/trips/{id}/items/{item}/alternate</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>[실측] 구현 · 쓰기(스위치)</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>항목을 다른 안으로 — 현재 판 번호를 서버에서 읽어 보낸다</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>MCP</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>tripilot_choose_proposal</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>POST /v1/web/trips/{id}/proposals/{proposal}/choose</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>[실측] 구현 · 쓰기(스위치)</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>대기 제안에 답(안을 고르거나 원래대로)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="46" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>MCP</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>tripilot_rollback</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>POST /v1/web/trips/{id}/rollback</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>[실측] 구현 · 쓰기(스위치)</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>옛 판으로 되돌리기</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="46" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>MCP</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>tripilot_submit_itinerary</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>POST /v1/web/trips</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>[실측] 구현 · 쓰기(스위치)</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>AI 가 만든 일정을 서버가 판정(영업시간·이동·동선·밀도)하고 통과하면 내 여행으로 등록</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="46" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>MCP</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>tripilot_plan_trip</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>POST /v1/web/trip-intakes → …/plan</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>[실측] 구현 · 쓰기(스위치)</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>서버의 일정 생성기가 짜서 판정을 통과한 것만 등록</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>MCP</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>접속 방식</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>원격 /mcp/ (Streamable HTTP) · 로컬 stdio 프록시</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>[실측] 구현</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>사용자 키(Authorization: Bearer 또는 X-User-Key)로 본인 여행만 열린다. 키가 없거나 틀리면 연결 단계에서 401. 도구에 customer_id 인자가 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>MCP</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>쓰기 스위치</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>config/guardrails.yaml → travel.mcp.write_enabled</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>[실측] false (기본 꺼짐)</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>꺼져 있으면 읽기 5개만 보인다. 켜면 쓰기 7개가 보인다 — 바뀌는 것은 일정뿐(되돌리기 가능), 결제·업체 예약은 안 한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="46" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>MCP</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
           <t>모듈 토글</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>config/project.yaml → modules.mcp.enabled</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>[실측] true</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>요청마다 확인한다 — 끄면 404</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>MCP</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>옛 도구 3개 (쇼핑몰 Case)</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>app/presentation/api/mcp.py</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>[실측] 연결 안 됨</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>이 표의 앞 판에 적혀 있던 list_cases(실제 이름 get_my_cases) · get_case_detail · open_support_case. 앱에 연결된 적이 없고 지금도 안 붙는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>MCP</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>외부 AI 종단 접속</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Claude · ChatGPT 등</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>[미확보]</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>MCP 프로토콜 클라이언트로 접속하는 시험은 통과(2026-10-02). 실제 외부 AI 로 붙은 기록은 아직 없다. OAuth 는 구현하지 않았다(헤더 키 방식)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>★ 결론 — A2A 는 프로토콜 표면(엔드포인트 5개)이 다 구현돼 있는데 ①실행기 토글이 꺼져 있고 ②여행 도메인에 원격 Team 이 없다. 「구현이 없다」가 아니라 「켜고 붙일 대상을 안 정했다」가 맞는 서술이다.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>확인한 범위 — config/project.yaml, app/presentation/a2a/, app/core/remote_team/, app/presentation/api/mcp.py 를 열어 봤다. 이 방법이 놓칠 수 있는 것: 런타임에 조립되는 등록이나 테스트 전용 배선은 정적 확인으로 안 잡힌다.</t>
+    <row r="31" ht="44" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>★ 결론 — MCP 는 읽기 5개 · 쓰기 7개(스위치 기본 꺼짐)로 만들어 고객 API 앱의 /mcp/ 에 붙였다(2026-10-02). 호출자는 사용자 키가 정하고 모든 도구가 웹 API 를 그대로 부르므로 새 규칙이 없다. 남은 것은 실제 외부 AI 로 붙은 기록과 OAuth 이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>확인한 범위 — config/project.yaml, app/presentation/a2a/, app/core/remote_team/, app/presentation/api/mcp.py(옛 도구), app/modules/travel_ops/mcp_server.py(지금의 MCP) 를 열어 봤고, 시험 tests/e2e/test_mcp_server.py(15건)가 MCP 프로토콜로 접속한다. 실제 서버에 MCP 클라이언트로 HTTP 접속해 /mcp/ 가 열리고 키 없이는 401 임을 확인했다. 이 방법이 놓칠 수 있는 것: 런타임에 조립되는 등록, 실제 외부 AI 의 동작.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A31:E31"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A17:E17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2856,6 +3227,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -3072,6 +3444,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
@@ -3117,6 +3490,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -3290,6 +3664,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
